--- a/source/guides/cdc/opioid-cds/ValueSet-therapies-indicating-end-of-life-care.xlsx
+++ b/source/guides/cdc/opioid-cds/ValueSet-therapies-indicating-end-of-life-care.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="68">
   <si>
     <t>Property</t>
   </si>
@@ -32,10 +32,16 @@
     <t>http://fhir.org/guides/cdc/opioid-cds/ValueSet/therapies-indicating-end-of-life-care</t>
   </si>
   <si>
+    <t>Identifier</t>
+  </si>
+  <si>
+    <t>OID:2.16.840.1.114222.48.43</t>
+  </si>
+  <si>
     <t>Version</t>
   </si>
   <si>
-    <t>2022.1.0</t>
+    <t>2022.1.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -144,6 +150,9 @@
   </si>
   <si>
     <t>http://snomed.info/sct|http://snomed.info/sct/731000124108/version/20230301</t>
+  </si>
+  <si>
+    <t>used-codesystem</t>
   </si>
   <si>
     <t>Level</t>
@@ -346,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -471,6 +480,14 @@
       </c>
       <c r="B15" t="s" s="2">
         <v>29</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -492,7 +509,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C1" t="s" s="1">
         <v>1</v>
@@ -500,29 +517,29 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -544,7 +561,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C1" t="s" s="1">
         <v>1</v>
@@ -552,29 +569,29 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -596,7 +613,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C1" t="s" s="1">
         <v>1</v>
@@ -604,29 +621,29 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -648,7 +665,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C1" t="s" s="1">
         <v>1</v>
@@ -656,29 +673,29 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -688,12 +705,12 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B1" t="s" s="1">
         <v>1</v>
@@ -701,10 +718,18 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>41</v>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -719,214 +744,214 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
+        <v>45</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>46</v>
+      </c>
+      <c r="C1" t="s" s="1">
         <v>42</v>
       </c>
-      <c r="B1" t="s" s="1">
-        <v>43</v>
-      </c>
-      <c r="C1" t="s" s="1">
-        <v>40</v>
-      </c>
       <c r="D1" t="s" s="1">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F1" t="s" s="1">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G1" t="s" s="1">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F2" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E3" t="s" s="2">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F3" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E4" t="s" s="2">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F4" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E5" t="s" s="2">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F5" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="E6" t="s" s="2">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F6" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E7" t="s" s="2">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F7" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E8" t="s" s="2">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F8" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E9" t="s" s="2">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F9" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E10" t="s" s="2">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F10" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
